--- a/sample-format/teiAndEnrollmentPost.xlsx
+++ b/sample-format/teiAndEnrollmentPost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mithilesh Thakur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitHub_source_code\excel_to_Json_Converter_angularJS\sample-format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562E6DDA-95FA-47A0-BD4E-16933A071F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F8D593-BCC7-42AE-A43B-9700495C2506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{526A35D4-64F2-4405-96E1-7020D529C647}"/>
   </bookViews>
@@ -555,11 +555,11 @@
     <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.1796875" customWidth="1"/>
+    <col min="7" max="7" width="22.6328125" customWidth="1"/>
+    <col min="8" max="8" width="20.6328125" customWidth="1"/>
     <col min="9" max="9" width="21.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
